--- a/4P_Index_Decret_2021-1115_CENPOLMAR.xlsx
+++ b/4P_Index_Decret_2021-1115_CENPOLMAR.xlsx
@@ -55,12 +55,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -428,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -573,77 +570,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Decree No. 2021-1115 of 25 August 2021 establishing the National Marine Pollution Response Coordination Centre (CENPOLMAR)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hassmar.gouv.sn/sites/default/files/reglementations/Decret%20CENPOLMAR_0.pdf</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Creates CENPOLMAR within HASSMAR as operational coordination body for marine hydrocarbon pollution response. Does not mention plastics or regulate plastic waste. EXCLUDED from instrument coding per strict plastics relevance filter — see Arrêté 07022/2009 (POLMAR) for marine waste provisions.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Presidential decree of 25 August 2021 establishing national operational centre within HASSMAR. Published Official Gazette No. 7470 of 13 November 2021. Executive regulation (≠1.0 law).</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>fisheries, environment, industry, water</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>disposal</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Art. 12: CENPOLMAR resources from HASSMAR budget, grants, private-sector services, exceptional contributions, donations and international cooperation.</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>EXCLUDED: No instruments coded. Policy fails strict plastics relevance filter (hydrocarbon marine pollution only; no plastics, EPR, bans, or municipal waste planning). Code marine plastic provisions under POLMAR (Order 07022/2009) instead.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
